--- a/s_expr_help_ru.xlsx
+++ b/s_expr_help_ru.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="96">
   <si>
     <t xml:space="preserve">Категория</t>
   </si>
@@ -269,6 +269,45 @@
   </si>
   <si>
     <t xml:space="preserve">Стандартный Lisp-стиль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Константы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnvFunction::Constant(std::f32::consts::PI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Число Пи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAU, TWOPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnvFunction::Constant(std::f32::consts::TAU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Число Тау, равное 2*Пи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnvFunction::Constant(std::f32::consts::E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Число Эйлера, основание натурального логарифма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnvFunction::Constant(1.618033988749895)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Число Фи, золотое сечение</t>
   </si>
 </sst>
 </file>
@@ -309,12 +348,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -330,26 +375,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF111111"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF333333"/>
-        <bgColor rgb="FF1C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C1C1C"/>
-        <bgColor rgb="FF111111"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF111111"/>
-        <bgColor rgb="FF1C1C1C"/>
+        <bgColor rgb="FF333300"/>
       </patternFill>
     </fill>
   </fills>
@@ -450,24 +477,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -475,11 +502,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -487,31 +518,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -519,31 +538,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -551,11 +562,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -620,8 +627,8 @@
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111111"/>
-      <rgbColor rgb="FF1C1C1C"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
@@ -808,74 +815,77 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="30.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.96"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="2" width="8.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+    <row r="4" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="10" t="s">
@@ -884,120 +894,120 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16" t="s">
+    <row r="6" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
+    <row r="8" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
+    <row r="10" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="18" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+    <row r="12" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
@@ -1006,173 +1016,266 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24" t="s">
+    <row r="14" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="21" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+    <row r="16" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17"/>
-      <c r="B18" s="16" t="s">
+    <row r="18" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17"/>
-      <c r="B20" s="16" t="s">
+    <row r="20" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
-      <c r="B22" s="16" t="s">
+    <row r="22" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="1" t="s">
         <v>82</v>
       </c>
     </row>
+    <row r="24" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" s="6" customFormat="true" ht="9.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+    </row>
+    <row r="30" s="6" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+    </row>
+    <row r="32" s="6" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+    </row>
+    <row r="34" s="6" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
